--- a/test/round00.xlsx
+++ b/test/round00.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="24960" windowHeight="12720"/>
   </bookViews>
   <sheets>
-    <sheet name="round00" sheetId="1" r:id="rId1"/>
+    <sheet name="wide" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -146,7 +146,7 @@
   </numFmts>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -155,8 +155,9 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -605,22 +606,20 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -629,7 +628,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -754,11 +753,9 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -812,221 +809,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1036,7 +819,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1046,39 +829,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1157,210 +940,283 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.8181818181818" customWidth="1"/>
+    <col min="1" max="1" width="16.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="12.6666666666667"/>
+    <col min="5" max="5" width="12.6666666666667"/>
+    <col min="7" max="7" width="12.6666666666667"/>
+    <col min="9" max="9" width="12.6666666666667"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="12.75" customWidth="1"/>
+    <col min="13" max="13" width="12.6666666666667"/>
+    <col min="15" max="15" width="12.6666666666667"/>
+    <col min="17" max="17" width="12.6666666666667"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" spans="1:15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="14.5" spans="1:15">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" s="1">
         <v>117</v>
       </c>
       <c r="C2" s="1">
-        <v>95</v>
+        <v>95.33333333</v>
       </c>
       <c r="D2" s="1">
         <v>189</v>
       </c>
       <c r="E2" s="1">
-        <v>133</v>
+        <v>132.33333337</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -1384,7 +1240,7 @@
         <v>144</v>
       </c>
       <c r="M2" s="1">
-        <v>111</v>
+        <v>111.333333333</v>
       </c>
       <c r="N2" s="1">
         <v>250</v>
@@ -1393,8 +1249,8 @@
         <v>173</v>
       </c>
     </row>
-    <row r="3" ht="14.5" spans="1:15">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="1">
@@ -1425,7 +1281,7 @@
         <v>77</v>
       </c>
       <c r="K3" s="1">
-        <v>63</v>
+        <v>62.66666667</v>
       </c>
       <c r="L3" s="1">
         <v>68</v>
@@ -1437,18 +1293,18 @@
         <v>333</v>
       </c>
       <c r="O3" s="1">
-        <v>252</v>
+        <v>252.3333333</v>
       </c>
     </row>
-    <row r="4" ht="14.5" spans="1:15">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="1">
         <v>156</v>
       </c>
       <c r="C4" s="1">
-        <v>97</v>
+        <v>97.33333334</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -1487,21 +1343,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="14.5" spans="1:15">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="1">
         <v>207</v>
       </c>
       <c r="C5" s="1">
-        <v>113</v>
+        <v>113.33333333</v>
       </c>
       <c r="D5" s="1">
         <v>117</v>
       </c>
       <c r="E5" s="1">
-        <v>88</v>
+        <v>87.66666667</v>
       </c>
       <c r="F5" s="1">
         <v>106</v>
@@ -1513,13 +1369,13 @@
         <v>150</v>
       </c>
       <c r="I5" s="1">
-        <v>114</v>
+        <v>113.66666667</v>
       </c>
       <c r="J5" s="1">
         <v>120</v>
       </c>
       <c r="K5" s="1">
-        <v>115</v>
+        <v>115.3333333</v>
       </c>
       <c r="L5" s="1">
         <v>0</v>
@@ -1534,68 +1390,68 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="14.5" spans="1:15">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="1">
         <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>11</v>
+        <v>10.333333334</v>
       </c>
       <c r="D6" s="1">
         <v>34</v>
       </c>
       <c r="E6" s="1">
-        <v>28</v>
+        <v>27.66666667</v>
       </c>
       <c r="F6" s="1">
         <v>28</v>
       </c>
       <c r="G6" s="1">
-        <v>22</v>
+        <v>21.66666667</v>
       </c>
       <c r="H6" s="1">
         <v>23</v>
       </c>
       <c r="I6" s="1">
-        <v>15</v>
+        <v>15.33333333</v>
       </c>
       <c r="J6" s="1">
         <v>60</v>
       </c>
       <c r="K6" s="1">
-        <v>49</v>
+        <v>49.33333333</v>
       </c>
       <c r="L6" s="1">
         <v>115</v>
       </c>
       <c r="M6" s="1">
-        <v>88</v>
+        <v>88.33333333</v>
       </c>
       <c r="N6" s="1">
         <v>374</v>
       </c>
       <c r="O6" s="1">
-        <v>277</v>
+        <v>276.6666667</v>
       </c>
     </row>
-    <row r="7" ht="14.5" spans="1:15">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="1">
         <v>200</v>
       </c>
       <c r="C7" s="1">
-        <v>157</v>
+        <v>156.33333334</v>
       </c>
       <c r="D7" s="1">
         <v>200</v>
       </c>
       <c r="E7" s="1">
-        <v>161</v>
+        <v>160.33333334</v>
       </c>
       <c r="F7" s="1">
         <v>297</v>
@@ -1607,7 +1463,7 @@
         <v>3</v>
       </c>
       <c r="I7" s="1">
-        <v>2</v>
+        <v>2.333333333</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
@@ -1628,8 +1484,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="14.5" spans="1:15">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="1">
@@ -1648,7 +1504,7 @@
         <v>261</v>
       </c>
       <c r="G8" s="1">
-        <v>189</v>
+        <v>189.3333333</v>
       </c>
       <c r="H8" s="1">
         <v>186</v>
@@ -1675,15 +1531,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="14.5" spans="1:15">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="1">
         <v>118</v>
       </c>
       <c r="C9" s="1">
-        <v>88</v>
+        <v>87.33333334</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -1707,13 +1563,13 @@
         <v>5</v>
       </c>
       <c r="K9" s="1">
-        <v>4</v>
+        <v>3.666666667</v>
       </c>
       <c r="L9" s="1">
         <v>381</v>
       </c>
       <c r="M9" s="1">
-        <v>276</v>
+        <v>276.6666666</v>
       </c>
       <c r="N9" s="1">
         <v>60</v>
@@ -1722,8 +1578,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" ht="14.5" spans="1:15">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="1">
@@ -1748,7 +1604,7 @@
         <v>217</v>
       </c>
       <c r="I10" s="1">
-        <v>174</v>
+        <v>174.3333333</v>
       </c>
       <c r="J10" s="1">
         <v>233</v>
@@ -1769,15 +1625,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="14.5" spans="1:15">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="1">
         <v>60</v>
       </c>
       <c r="C11" s="1">
-        <v>26</v>
+        <v>25.66666667</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -1801,7 +1657,7 @@
         <v>142</v>
       </c>
       <c r="K11" s="1">
-        <v>112</v>
+        <v>111.66666667</v>
       </c>
       <c r="L11" s="1">
         <v>57</v>
@@ -1813,24 +1669,24 @@
         <v>169</v>
       </c>
       <c r="O11" s="1">
-        <v>139</v>
+        <v>139.33333333</v>
       </c>
     </row>
-    <row r="12" ht="14.5" spans="1:15">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="1">
         <v>200</v>
       </c>
       <c r="C12" s="1">
-        <v>163</v>
+        <v>162.33333334</v>
       </c>
       <c r="D12" s="1">
         <v>50</v>
       </c>
       <c r="E12" s="1">
-        <v>40</v>
+        <v>40.333333333</v>
       </c>
       <c r="F12" s="1">
         <v>52</v>
@@ -1848,36 +1704,36 @@
         <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>1</v>
+        <v>0.666666667</v>
       </c>
       <c r="L12" s="1">
         <v>282</v>
       </c>
       <c r="M12" s="1">
-        <v>197</v>
+        <v>197.33333333</v>
       </c>
       <c r="N12" s="1">
         <v>77</v>
       </c>
       <c r="O12" s="1">
-        <v>51</v>
+        <v>51.33333333</v>
       </c>
     </row>
-    <row r="13" ht="14.5" spans="1:15">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
         <v>26</v>
       </c>
       <c r="B13" s="1">
         <v>100</v>
       </c>
       <c r="C13" s="1">
-        <v>80</v>
+        <v>79.66666667</v>
       </c>
       <c r="D13" s="1">
         <v>400</v>
       </c>
       <c r="E13" s="1">
-        <v>261</v>
+        <v>260.33333337</v>
       </c>
       <c r="F13" s="1">
         <v>199</v>
@@ -1910,27 +1766,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="14.5" spans="1:15">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="1">
         <v>101</v>
       </c>
       <c r="C14" s="1">
-        <v>77</v>
+        <v>77.33333333</v>
       </c>
       <c r="D14" s="1">
         <v>103</v>
       </c>
       <c r="E14" s="1">
-        <v>85</v>
+        <v>84.66666667</v>
       </c>
       <c r="F14" s="1">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="G14" s="1">
-        <v>83</v>
+        <v>83.33333333</v>
       </c>
       <c r="H14" s="1">
         <v>51</v>
@@ -1942,23 +1798,23 @@
         <v>151</v>
       </c>
       <c r="K14" s="1">
-        <v>86</v>
+        <v>85.66666667</v>
       </c>
       <c r="L14" s="1">
         <v>139</v>
       </c>
       <c r="M14" s="1">
-        <v>96</v>
+        <v>96.333333333</v>
       </c>
       <c r="N14" s="1">
         <v>53</v>
       </c>
       <c r="O14" s="1">
-        <v>43</v>
+        <v>43.33333333</v>
       </c>
     </row>
-    <row r="15" ht="14.5" spans="1:15">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="1">
@@ -1971,10 +1827,10 @@
         <v>127</v>
       </c>
       <c r="E15" s="1">
-        <v>91</v>
+        <v>91.66666666</v>
       </c>
       <c r="F15" s="1">
-        <v>163</v>
+        <v>212</v>
       </c>
       <c r="G15" s="1">
         <v>146</v>
@@ -1983,7 +1839,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="1">
-        <v>62</v>
+        <v>61.66666667</v>
       </c>
       <c r="J15" s="1">
         <v>99</v>
@@ -2004,27 +1860,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="14.5" spans="1:15">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="1">
         <v>253</v>
       </c>
       <c r="C16" s="1">
-        <v>192</v>
+        <v>191.33333337</v>
       </c>
       <c r="D16" s="1">
         <v>148</v>
       </c>
       <c r="E16" s="1">
-        <v>109</v>
+        <v>109.33333333</v>
       </c>
       <c r="F16" s="1">
-        <v>200</v>
+        <v>98</v>
       </c>
       <c r="G16" s="1">
-        <v>62</v>
+        <v>62.33333333</v>
       </c>
       <c r="H16" s="1">
         <v>201</v>
@@ -2051,33 +1907,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="14.5" spans="1:15">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="1">
         <v>188</v>
       </c>
       <c r="C17" s="1">
-        <v>134</v>
+        <v>134.66666666</v>
       </c>
       <c r="D17" s="1">
         <v>228</v>
       </c>
       <c r="E17" s="1">
-        <v>182</v>
+        <v>181.33333334</v>
       </c>
       <c r="F17" s="1">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="G17" s="1">
-        <v>64</v>
+        <v>64.33333333</v>
       </c>
       <c r="H17" s="1">
         <v>108</v>
       </c>
       <c r="I17" s="1">
-        <v>90</v>
+        <v>89.66666667</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
@@ -2098,8 +1954,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="14.5" spans="1:15">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:15">
+      <c r="A18" t="s">
         <v>31</v>
       </c>
       <c r="B18" s="1">
@@ -2115,22 +1971,22 @@
         <v>104</v>
       </c>
       <c r="F18" s="1">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G18" s="1">
-        <v>68</v>
+        <v>67.66666667</v>
       </c>
       <c r="H18" s="1">
         <v>4</v>
       </c>
       <c r="I18" s="1">
-        <v>3</v>
+        <v>3.333333333</v>
       </c>
       <c r="J18" s="1">
         <v>167</v>
       </c>
       <c r="K18" s="1">
-        <v>121</v>
+        <v>121.3333333</v>
       </c>
       <c r="L18" s="1">
         <v>129</v>
@@ -2145,15 +2001,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="14.5" spans="1:15">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:15">
+      <c r="A19" t="s">
         <v>32</v>
       </c>
       <c r="B19" s="1">
         <v>56</v>
       </c>
       <c r="C19" s="1">
-        <v>43</v>
+        <v>43.66666666</v>
       </c>
       <c r="D19" s="1">
         <v>119</v>
@@ -2162,16 +2018,16 @@
         <v>97</v>
       </c>
       <c r="F19" s="1">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="G19" s="1">
-        <v>40</v>
+        <v>40.33333333</v>
       </c>
       <c r="H19" s="1">
         <v>220</v>
       </c>
       <c r="I19" s="1">
-        <v>144</v>
+        <v>144.66666663</v>
       </c>
       <c r="J19" s="1">
         <v>229</v>
@@ -2192,8 +2048,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="14.5" spans="1:15">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:15">
+      <c r="A20" t="s">
         <v>33</v>
       </c>
       <c r="B20" s="1">
@@ -2209,10 +2065,10 @@
         <v>37</v>
       </c>
       <c r="F20" s="1">
-        <v>172</v>
+        <v>66</v>
       </c>
       <c r="G20" s="1">
-        <v>27</v>
+        <v>26.66666667</v>
       </c>
       <c r="H20" s="1">
         <v>199</v>
@@ -2224,13 +2080,13 @@
         <v>123</v>
       </c>
       <c r="K20" s="1">
-        <v>52</v>
+        <v>52.333333333</v>
       </c>
       <c r="L20" s="1">
         <v>252</v>
       </c>
       <c r="M20" s="1">
-        <v>135</v>
+        <v>134.6666667</v>
       </c>
       <c r="N20" s="1">
         <v>0</v>
@@ -2239,24 +2095,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="14.5" spans="1:15">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:15">
+      <c r="A21" t="s">
         <v>34</v>
       </c>
       <c r="B21" s="1">
         <v>100</v>
       </c>
       <c r="C21" s="1">
-        <v>74</v>
+        <v>73.66666667</v>
       </c>
       <c r="D21" s="1">
         <v>108</v>
       </c>
       <c r="E21" s="1">
-        <v>91</v>
+        <v>90.66666667</v>
       </c>
       <c r="F21" s="1">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="G21" s="1">
         <v>8</v>
@@ -2277,20 +2133,14 @@
         <v>166</v>
       </c>
       <c r="M21" s="1">
-        <v>127</v>
+        <v>126.66666667</v>
       </c>
       <c r="N21" s="1">
         <v>253</v>
       </c>
       <c r="O21" s="1">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="22" ht="14.5" spans="1:15">
-      <c r="H22" s="1"/>
-    </row>
-    <row r="26" ht="14.5" spans="1:15">
-      <c r="I26" s="1"/>
+        <v>190.66666667</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
